--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484881_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484881_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0008</v>
+        <v>6.5473</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8951</v>
+        <v>4.759</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1057</v>
+        <v>1.7883</v>
       </c>
       <c r="G2" t="n">
         <v>4.2536</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4867</v>
+        <v>1.0331</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6895</v>
+        <v>0.5534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7972</v>
+        <v>0.4797</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0604</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>C. SEGUI HEREDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7419</v>
+        <v>4.2389</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3964</v>
+        <v>1.9067</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3454</v>
+        <v>2.3322</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2452</v>
+        <v>1.7554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5916</v>
+        <v>-0.8593</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6536</v>
+        <v>2.6148</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2041</v>
+        <v>2.1257</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8281</v>
+        <v>0.1173</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.624</v>
+        <v>2.0083</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0411</v>
+        <v>-0.3702</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2365</v>
+        <v>-0.9767</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2776</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0192</v>
+        <v>1.1322</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
         <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4209</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8905</v>
+        <v>-0.1998</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4696</v>
+        <v>-0.3168</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9434</v>
+        <v>1.8678</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3018</v>
+        <v>1.8678</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. SEGUI HEREDIA</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2805</v>
+        <v>3.4516</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1071</v>
+        <v>2.0268</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1735</v>
+        <v>1.4248</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7554</v>
+        <v>1.2452</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8593</v>
+        <v>0.5916</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6148</v>
+        <v>0.6536</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1257</v>
+        <v>1.2041</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1173</v>
+        <v>1.8281</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0083</v>
+        <v>-0.624</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3702</v>
+        <v>0.0411</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9767</v>
+        <v>-1.2365</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6064000000000001</v>
+        <v>1.2776</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1322</v>
+        <v>3.0192</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>3.0192</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4749</v>
+        <v>0.1306</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9994</v>
+        <v>0.5209</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4755</v>
+        <v>-0.3903</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8678</v>
+        <v>-0.9434</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8678</v>
+        <v>0.3018</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9728</v>
+        <v>3.0232</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0132</v>
+        <v>0.1431</v>
       </c>
       <c r="F5" t="n">
-        <v>2.986</v>
+        <v>2.8802</v>
       </c>
       <c r="G5" t="n">
         <v>1.8524</v>
@@ -844,13 +844,13 @@
         <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3656</v>
+        <v>0.416</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2409</v>
+        <v>0.3972</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1247</v>
+        <v>0.0189</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5601</v>
+        <v>1.8054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.447</v>
+        <v>0.7981</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1131</v>
+        <v>1.0073</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7028</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0399</v>
+        <v>1.2851</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7483</v>
+        <v>1.0993</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2916</v>
+        <v>0.1858</v>
       </c>
       <c r="V6" t="n">
         <v>-0.664</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.951</v>
+        <v>0.9388</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5599</v>
+        <v>-0.5986</v>
       </c>
       <c r="F7" t="n">
-        <v>1.511</v>
+        <v>1.5374</v>
       </c>
       <c r="G7" t="n">
         <v>1.1796</v>
@@ -1000,13 +1000,13 @@
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7753</v>
+        <v>0.7631</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6895</v>
+        <v>0.6508</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0859</v>
+        <v>0.1123</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0604</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.0165</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9788</v>
+        <v>-0.5303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.441</v>
+        <v>0.5468</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1722</v>
@@ -1078,13 +1078,13 @@
         <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.743</v>
+        <v>-0.1887</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4115</v>
+        <v>0.037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3315</v>
+        <v>-0.2257</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5512</v>
+        <v>-0.519</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3455</v>
+        <v>-0.1821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7943</v>
+        <v>-0.3369</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1947</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1088</v>
+        <v>0.396</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3035</v>
+        <v>0.171</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8055</v>
+        <v>1.0554</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3858</v>
+        <v>1.0142</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1913</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6108</v>
+        <v>-0.4883</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.277</v>
+        <v>-0.6182</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8878</v>
+        <v>0.1299</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1568</v>
+        <v>-0.5955</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9886</v>
+        <v>-0.2939</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1682</v>
+        <v>-0.3016</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9471</v>
+        <v>-0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3056</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5719</v>
+        <v>-1.1694</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1821</v>
+        <v>0.8347</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3898</v>
+        <v>-2.0041</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.1294</v>
       </c>
       <c r="H10" t="n">
-        <v>0.396</v>
+        <v>-1.4094</v>
       </c>
       <c r="I10" t="n">
-        <v>0.171</v>
+        <v>1.5389</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0554</v>
+        <v>1.2678</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0142</v>
+        <v>-0.2058</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0411</v>
+        <v>1.4736</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4883</v>
+        <v>-1.1384</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6182</v>
+        <v>-1.2036</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1299</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6484</v>
+        <v>-0.4464</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2939</v>
+        <v>0.2085</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3545</v>
+        <v>-0.6548</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3018</v>
+        <v>-2.5508</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3018</v>
+        <v>-1.9092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0094</v>
+        <v>-1.337</v>
       </c>
       <c r="E11" t="n">
-        <v>1.127</v>
+        <v>-2.1048</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1364</v>
+        <v>0.7678</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1294</v>
+        <v>-0.1947</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4094</v>
+        <v>0.1088</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5389</v>
+        <v>-0.3035</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2678</v>
+        <v>-0.8055</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2058</v>
+        <v>0.3858</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4736</v>
+        <v>-1.1913</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1384</v>
+        <v>0.6108</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2036</v>
+        <v>-0.277</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.8878</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6983</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2863</v>
+        <v>1.371</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5008</v>
+        <v>1.2293</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7871</v>
+        <v>0.1417</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5508</v>
+        <v>-1.9471</v>
       </c>
       <c r="W11" t="n">
         <v>-0.6415999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9092</v>
+        <v>-1.3056</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5263</v>
+        <v>-2.2848</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0217</v>
+        <v>-1.8067</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5046</v>
+        <v>-0.4781</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4331</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1123</v>
+        <v>0.1292</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0559</v>
+        <v>0.1591</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0564</v>
+        <v>-0.0299</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1696</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.831</v>
+        <v>-4.3502</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0527</v>
+        <v>-5.5454</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2217</v>
+        <v>1.1953</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5339</v>
@@ -1468,13 +1468,13 @@
         <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5143</v>
+        <v>0.9952</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3709</v>
+        <v>0.8782</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1435</v>
+        <v>0.117</v>
       </c>
       <c r="V13" t="n">
         <v>1.2642</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.479500000000002</v>
+        <v>10.3613</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.181299999999999</v>
+        <v>-0.299500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6609</v>
+        <v>10.661</v>
       </c>
       <c r="G14" t="n">
-        <v>4.945900000000001</v>
+        <v>4.945900000000003</v>
       </c>
       <c r="H14" t="n">
         <v>-5.7677</v>
@@ -1519,22 +1519,22 @@
         <v>10.7138</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5571</v>
+        <v>5.557099999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>1.557000000000001</v>
+        <v>1.557</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9998</v>
+        <v>3.999799999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-0.6110000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.3248</v>
+        <v>-7.324800000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>6.7139</v>
+        <v>6.713900000000001</v>
       </c>
       <c r="P14" t="n">
         <v>6.604500000000002</v>
@@ -1546,13 +1546,13 @@
         <v>21.7005</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4946</v>
+        <v>4.376099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.358300000000001</v>
+        <v>5.239999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8634999999999999</v>
+        <v>-0.8637000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-5.5655</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7533</v>
+        <v>5.9848</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2603</v>
+        <v>3.5782</v>
       </c>
       <c r="F15" t="n">
-        <v>2.493</v>
+        <v>2.4065</v>
       </c>
       <c r="G15" t="n">
         <v>1.782</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7183</v>
+        <v>0.9499</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5524</v>
+        <v>0.8704</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1659</v>
+        <v>0.0795</v>
       </c>
       <c r="V15" t="n">
         <v>1.7433</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.043</v>
+        <v>1.2475</v>
       </c>
       <c r="E17" t="n">
         <v>1.6783</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6354</v>
+        <v>-0.4308</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2784</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1387</v>
+        <v>0.0659</v>
       </c>
       <c r="T17" t="n">
         <v>0.3709</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5095</v>
+        <v>-0.305</v>
       </c>
       <c r="V17" t="n">
         <v>2.0261</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6803</v>
+        <v>0.617</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8228</v>
+        <v>0.617</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5031</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7323</v>
+        <v>0.617</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2418</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9741</v>
+        <v>0.617</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4375</v>
+        <v>0.617</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5112</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9487</v>
+        <v>0.617</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2947</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2693</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9746</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.5853</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.661</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3867</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5401</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1533</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.6111</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.7356</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>V. CAMBRA NADAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.617</v>
+        <v>0.2499</v>
       </c>
       <c r="E19" t="n">
-        <v>0.617</v>
+        <v>0.1098</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1401</v>
       </c>
       <c r="G19" t="n">
-        <v>0.617</v>
+        <v>-0.1515</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.617</v>
+        <v>-0.4113</v>
       </c>
       <c r="J19" t="n">
-        <v>0.617</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.617</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.1515</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.2126</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. CAMBRA NADAL</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.126</v>
+        <v>-0.2806</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0123</v>
+        <v>-1.9458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1136</v>
+        <v>1.6652</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1515</v>
+        <v>1.94</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2598</v>
+        <v>0.0219</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4113</v>
+        <v>1.9181</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.837</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.1534</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6836</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1515</v>
+        <v>1.103</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2598</v>
+        <v>-0.1315</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4113</v>
+        <v>1.2344</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0888</v>
+        <v>-0.9186</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0123</v>
+        <v>0.0477</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0764</v>
+        <v>-0.9664</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.487</v>
+        <v>-0.7103</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6278</v>
+        <v>-2.1869</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1408</v>
+        <v>1.4766</v>
       </c>
       <c r="G21" t="n">
-        <v>1.94</v>
+        <v>-0.7323</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0219</v>
+        <v>0.2418</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9181</v>
+        <v>-0.9741</v>
       </c>
       <c r="J21" t="n">
-        <v>0.837</v>
+        <v>-0.4375</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1534</v>
+        <v>1.5112</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6836</v>
+        <v>-1.9487</v>
       </c>
       <c r="M21" t="n">
-        <v>1.103</v>
+        <v>-0.2947</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1315</v>
+        <v>-1.2693</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2344</v>
+        <v>0.9746</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3209</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8305</v>
+        <v>-5.661</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.125</v>
+        <v>-0.0038</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6343</v>
+        <v>0.176</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4907</v>
+        <v>-0.1798</v>
       </c>
       <c r="V21" t="n">
-        <v>0.019</v>
+        <v>3.6111</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.7356</v>
       </c>
       <c r="X21" t="n">
-        <v>0.019</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.986</v>
+        <v>-1.5857</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5589</v>
+        <v>-1.536</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4271</v>
+        <v>-0.0497</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8895</v>
+        <v>-2.0945</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9391</v>
+        <v>0.4837</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0496</v>
+        <v>-2.5781</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0867</v>
+        <v>-1.1312</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3789</v>
+        <v>0.1268</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7077</v>
+        <v>-1.258</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1972</v>
+        <v>-0.9633</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4398</v>
+        <v>0.3569</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7574</v>
+        <v>-1.3202</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3468</v>
+        <v>-0.3966</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1735</v>
+        <v>-0.178</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1734</v>
+        <v>-0.2186</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.9054</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.9054</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0344</v>
+        <v>-1.8008</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8283</v>
+        <v>-1.5589</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2061</v>
+        <v>-0.2419</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0945</v>
+        <v>0.8895</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4837</v>
+        <v>0.9391</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5781</v>
+        <v>-0.0496</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1312</v>
+        <v>2.0867</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1268</v>
+        <v>1.3789</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.258</v>
+        <v>0.7077</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9633</v>
+        <v>-1.1972</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3569</v>
+        <v>-0.4398</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3202</v>
+        <v>-0.7574</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1322</v>
+        <v>-2.8305</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.1617</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4703</v>
+        <v>-0.1735</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.375</v>
+        <v>0.0118</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9054</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9054</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.688</v>
+        <v>-1.8917</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4713</v>
+        <v>-3.2764</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7833</v>
+        <v>1.3847</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0424</v>
@@ -2326,13 +2326,13 @@
         <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8982</v>
+        <v>-0.102</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0029</v>
+        <v>0.1978</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9011</v>
+        <v>-0.2997</v>
       </c>
       <c r="V24" t="n">
         <v>0.5171</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1264</v>
+        <v>-3.4271</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3453</v>
+        <v>-1.5401</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7811</v>
+        <v>-1.8869</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6539</v>
@@ -2404,13 +2404,13 @@
         <v>1.6983</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2839</v>
+        <v>-0.5846</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1735</v>
+        <v>-0.3683</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1105</v>
+        <v>-0.2163</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9434</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.645200000000001</v>
+        <v>-7.2018</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.8423</v>
+        <v>-5.8679</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8029</v>
+        <v>-1.3338</v>
       </c>
       <c r="G26" t="n">
         <v>-5.4894</v>
@@ -2482,13 +2482,13 @@
         <v>1.6983</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0504</v>
+        <v>-0.6069</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1634</v>
+        <v>-0.1891</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8869</v>
+        <v>-0.4178</v>
       </c>
       <c r="V26" t="n">
         <v>-1.6715</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.479600000000001</v>
+        <v>-7.531000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.661</v>
+        <v>-10.6609</v>
       </c>
       <c r="F27" t="n">
-        <v>1.181199999999999</v>
+        <v>3.13</v>
       </c>
       <c r="G27" t="n">
         <v>-4.946099999999999</v>
@@ -2551,7 +2551,7 @@
         <v>-3.9999</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.604500000000002</v>
+        <v>-6.6045</v>
       </c>
       <c r="Q27" t="n">
         <v>-21.7005</v>
@@ -2560,13 +2560,13 @@
         <v>15.096</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.4945</v>
+        <v>-1.5458</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8636000000000001</v>
+        <v>0.8636999999999997</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.3581</v>
+        <v>-2.4094</v>
       </c>
       <c r="V27" t="n">
         <v>5.565499999999998</v>
